--- a/AAII_Financials/Quarterly/UNCRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UNCRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="92">
   <si>
     <t>UNCRY</t>
   </si>
@@ -656,75 +656,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -770,8 +773,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,8 +823,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +873,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -883,8 +895,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -930,8 +943,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -977,8 +993,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1024,8 +1043,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1071,8 +1093,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1087,8 +1112,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1134,8 +1160,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1181,8 +1210,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1200,8 +1232,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1247,8 +1280,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1294,8 +1330,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1341,8 +1380,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1388,8 +1430,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1435,8 +1480,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1482,8 +1530,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1529,8 +1580,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1576,8 +1630,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1623,8 +1680,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1670,8 +1730,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1717,8 +1780,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1764,8 +1830,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1811,8 +1880,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1858,8 +1930,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1905,8 +1980,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1952,60 +2030,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2023,8 +2107,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2042,431 +2127,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52398000</v>
+      </c>
+      <c r="E41" s="3">
         <v>55551700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45150900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>56497700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49094500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>47525900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42905100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42856300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53604400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70593400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>67548400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92460800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>83044800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>137306600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>119588500</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>168070400</v>
+      </c>
+      <c r="E42" s="3">
         <v>75102000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>130392200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>67901000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>154051700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>57767000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>112925800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>63952700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>134388700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58309400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>117141600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>62687300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>142597200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>63683200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>115244200</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2195800</v>
+      </c>
+      <c r="E43" s="3">
         <v>11392800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10879400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11146300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1852000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10140500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9224600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11074100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1478600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11940900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8755400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11999400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2105900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13646200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5372400</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>450900</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>458600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>596900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>865700</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E45" s="3">
         <v>265200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2039500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>274600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1114500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>971700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1730000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>525300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>653600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>384100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1475600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1268000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1539300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1223400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1593500</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>231598300</v>
+      </c>
+      <c r="E46" s="3">
         <v>142311800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200863000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>135819500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>215506800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>116405100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>175824600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>118408400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>199341000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>141227700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>204149400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>168415500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>256747800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>215859400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>263413500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>176389800</v>
+      </c>
+      <c r="E47" s="3">
         <v>286755400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>184898400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>283912900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>168938300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>198624100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>106921000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>201393000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>102108600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>180310700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>96296000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>161719900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>85996700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>161059300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>82631200</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9826300</v>
+      </c>
+      <c r="E48" s="3">
         <v>10100300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8168400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10225300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10362900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9468200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7234700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9834900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9598200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9872700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7985000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9366000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9755500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9881600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8315700</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3332600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3357500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3451900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3829600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3841500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2696700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2307700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2405800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2350800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2384300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2511300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2360300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2461800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2498900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2515800</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2512,8 +2625,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2559,55 +2675,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20814600</v>
+      </c>
+      <c r="E52" s="3">
         <v>20802500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14408800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15628300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16142100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15150200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6034800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15210800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14262300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14180600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6684000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12523300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12026200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12339200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6327900</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2653,55 +2775,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1064881800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1040199500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1021765900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1033151500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1010367600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>860284300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>811682400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>896173300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>856021600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>874504300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>867662200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>873882300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>920858100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>972758600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>916718000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2719,8 +2847,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2738,290 +2867,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>613446800</v>
+      </c>
+      <c r="E57" s="3">
         <v>697922300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>619893200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>706277100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>589627700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>616824500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>516687000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>647420300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>529282100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>635687800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>564108500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>643050400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>560995600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>729516500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>632470900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>120274200</v>
+      </c>
+      <c r="E58" s="3">
         <v>35582800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>91192900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>27939700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>103920100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>25491800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>72324300</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3">
         <v>90276400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>28584500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>61858100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28414500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>102796900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>35659500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>58473900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10061700</v>
+      </c>
+      <c r="E59" s="3">
         <v>3506300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11002700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3225400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11495000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2413500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9359100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>42644400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11992900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1885900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14383800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2326400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21097200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2492400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14165900</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>745406100</v>
+      </c>
+      <c r="E60" s="3">
         <v>737011400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>729852100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>737442200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>706711700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>644729800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>605110300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>680349100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>632534000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>666158200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>647174800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>673791300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>686153900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>767668400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>711146700</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>162821900</v>
+      </c>
+      <c r="E61" s="3">
         <v>117759700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>152080500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>116256000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>150755100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>101147900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>126685000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>100508600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>133862600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>98114100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>134993900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>97958300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>137288200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>96675400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>122982800</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>71738800</v>
+      </c>
+      <c r="E62" s="3">
         <v>106093600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>55618200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>98051200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>68236100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>43388500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10956600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44094400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19104300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>39467000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10382400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>35575800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25602600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>39092800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10566400</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3067,8 +3215,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3114,8 +3265,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3161,55 +3315,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>983976900</v>
+      </c>
+      <c r="E66" s="3">
         <v>960864800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>941797600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>951749400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>930017600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>789266100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>746622800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>824952000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>789407500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>803739300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>796651900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>807325400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>853140800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>903436500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>848857500</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3227,8 +3387,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3274,8 +3435,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3321,8 +3485,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3368,8 +3535,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3415,55 +3585,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>46645700</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>44831500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>41488000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2995000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>36313300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8643800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>36196300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>38654800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>35357000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>32253900</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3509,8 +3685,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3556,8 +3735,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3603,55 +3785,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>80455800</v>
+      </c>
+      <c r="E76" s="3">
         <v>78893100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>79501000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>80950400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>79886100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>70603100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>64645400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71036100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>66444900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>70579400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>70829000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>66390800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>67555700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>69144900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>67691600</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3697,60 +3885,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3796,8 +3990,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3815,8 +4012,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3862,8 +4060,11 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3909,8 +4110,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3956,8 +4160,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4003,8 +4210,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4050,8 +4260,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4097,8 +4310,11 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4144,8 +4360,11 @@
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4163,8 +4382,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4210,8 +4430,11 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4257,8 +4480,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4304,8 +4530,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4351,8 +4580,11 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4370,8 +4602,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4417,8 +4650,11 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4464,8 +4700,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4511,8 +4750,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4558,8 +4800,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4605,8 +4850,11 @@
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4652,8 +4900,11 @@
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4697,6 +4948,9 @@
         <v>4</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
